--- a/results/02_taxa_assemblage/artifacts/02_hindsight_updated_data.xlsx
+++ b/results/02_taxa_assemblage/artifacts/02_hindsight_updated_data.xlsx
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">

--- a/results/02_taxa_assemblage/artifacts/02_hindsight_updated_data.xlsx
+++ b/results/02_taxa_assemblage/artifacts/02_hindsight_updated_data.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +527,9 @@
           <t>010B</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -535,7 +537,9 @@
           <t>011A</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -591,7 +595,9 @@
           <t>018A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -647,7 +653,9 @@
           <t>026C</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -671,7 +679,9 @@
           <t>030ABC</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -687,7 +697,9 @@
           <t>033ABC</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -703,7 +715,9 @@
           <t>035C</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -711,7 +725,9 @@
           <t>036C</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -735,7 +751,9 @@
           <t>043ABC</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -815,7 +833,9 @@
           <t>058C</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -831,7 +851,9 @@
           <t>060B</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -839,7 +861,9 @@
           <t>064B</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -847,7 +871,9 @@
           <t>065C</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -855,7 +881,9 @@
           <t>066A</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -871,7 +899,9 @@
           <t>068B</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -895,7 +925,9 @@
           <t>071B</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -911,7 +943,9 @@
           <t>073C</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -927,9 +961,7 @@
           <t>075A</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -945,7 +977,9 @@
           <t>077B</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1073,7 +1107,9 @@
           <t>094C</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1097,7 +1133,9 @@
           <t>097ABC</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1105,7 +1143,9 @@
           <t>098C</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -1193,7 +1233,9 @@
           <t>109C</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -1201,7 +1243,9 @@
           <t xml:space="preserve">111C </t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -1265,7 +1309,9 @@
           <t>121C</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -1274,7 +1320,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -1299,7 +1345,9 @@
           <t>125A</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -1363,7 +1411,9 @@
           <t>133B</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -1411,7 +1461,9 @@
           <t>139B</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -1427,7 +1479,9 @@
           <t>141B</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -1499,7 +1553,9 @@
           <t>150B</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -1547,9 +1603,7 @@
           <t>A5</t>
         </is>
       </c>
-      <c r="B138" t="n">
-        <v>2</v>
-      </c>
+      <c r="B138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -1622,7 +1676,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -1639,9 +1693,7 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="B149" t="n">
-        <v>1</v>
-      </c>
+      <c r="B149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -1649,9 +1701,7 @@
           <t>S10</t>
         </is>
       </c>
-      <c r="B150" t="n">
-        <v>1</v>
-      </c>
+      <c r="B150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -1675,9 +1725,7 @@
           <t>S102</t>
         </is>
       </c>
-      <c r="B153" t="n">
-        <v>1</v>
-      </c>
+      <c r="B153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -1685,9 +1733,7 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="B154" t="n">
-        <v>1</v>
-      </c>
+      <c r="B154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -1695,9 +1741,7 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="B155" t="n">
-        <v>2</v>
-      </c>
+      <c r="B155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -1713,9 +1757,7 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="B157" t="n">
-        <v>1</v>
-      </c>
+      <c r="B157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -1739,9 +1781,7 @@
           <t>S17</t>
         </is>
       </c>
-      <c r="B160" t="n">
-        <v>2</v>
-      </c>
+      <c r="B160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -1749,9 +1789,7 @@
           <t>S18</t>
         </is>
       </c>
-      <c r="B161" t="n">
-        <v>1</v>
-      </c>
+      <c r="B161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -1759,9 +1797,7 @@
           <t>S19</t>
         </is>
       </c>
-      <c r="B162" t="n">
-        <v>2</v>
-      </c>
+      <c r="B162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -1777,9 +1813,7 @@
           <t>S21</t>
         </is>
       </c>
-      <c r="B164" t="n">
-        <v>1</v>
-      </c>
+      <c r="B164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -1787,9 +1821,7 @@
           <t>S21(5)</t>
         </is>
       </c>
-      <c r="B165" t="n">
-        <v>1</v>
-      </c>
+      <c r="B165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -1797,9 +1829,7 @@
           <t>S22</t>
         </is>
       </c>
-      <c r="B166" t="n">
-        <v>1</v>
-      </c>
+      <c r="B166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -1808,7 +1838,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
@@ -1817,9 +1847,7 @@
           <t>S24</t>
         </is>
       </c>
-      <c r="B168" t="n">
-        <v>1</v>
-      </c>
+      <c r="B168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -1828,7 +1856,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -1854,7 +1882,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -1863,9 +1891,7 @@
           <t>S28(5)</t>
         </is>
       </c>
-      <c r="B173" t="n">
-        <v>1</v>
-      </c>
+      <c r="B173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -1881,9 +1907,7 @@
           <t>S36</t>
         </is>
       </c>
-      <c r="B175" t="n">
-        <v>1</v>
-      </c>
+      <c r="B175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -1892,7 +1916,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -1902,7 +1926,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -1912,7 +1936,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -1921,9 +1945,7 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="B179" t="n">
-        <v>1</v>
-      </c>
+      <c r="B179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -1931,9 +1953,7 @@
           <t>S40</t>
         </is>
       </c>
-      <c r="B180" t="n">
-        <v>1</v>
-      </c>
+      <c r="B180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -2021,9 +2041,7 @@
           <t>S50</t>
         </is>
       </c>
-      <c r="B191" t="n">
-        <v>1</v>
-      </c>
+      <c r="B191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -2032,7 +2050,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -2087,9 +2105,7 @@
           <t>S57</t>
         </is>
       </c>
-      <c r="B198" t="n">
-        <v>1</v>
-      </c>
+      <c r="B198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -2097,9 +2113,7 @@
           <t>S58</t>
         </is>
       </c>
-      <c r="B199" t="n">
-        <v>1</v>
-      </c>
+      <c r="B199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -2107,9 +2121,7 @@
           <t>S59</t>
         </is>
       </c>
-      <c r="B200" t="n">
-        <v>1</v>
-      </c>
+      <c r="B200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -2158,7 +2170,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -2183,9 +2195,7 @@
           <t>S68</t>
         </is>
       </c>
-      <c r="B209" t="n">
-        <v>1</v>
-      </c>
+      <c r="B209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -2193,9 +2203,7 @@
           <t>S69</t>
         </is>
       </c>
-      <c r="B210" t="n">
-        <v>1</v>
-      </c>
+      <c r="B210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -2204,7 +2212,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212">
@@ -2223,9 +2231,7 @@
           <t>S74</t>
         </is>
       </c>
-      <c r="B213" t="n">
-        <v>1</v>
-      </c>
+      <c r="B213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -2241,9 +2247,7 @@
           <t>S79</t>
         </is>
       </c>
-      <c r="B215" t="n">
-        <v>1</v>
-      </c>
+      <c r="B215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -2251,9 +2255,7 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="B216" t="n">
-        <v>1</v>
-      </c>
+      <c r="B216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -2270,7 +2272,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -2279,9 +2281,7 @@
           <t>S82</t>
         </is>
       </c>
-      <c r="B219" t="n">
-        <v>1</v>
-      </c>
+      <c r="B219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
